--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -6,7 +6,7 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21ED0C93-A8DF-48A3-9022-E405BE4E7FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A45B7C-8484-47A8-8850-EA02003EFAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="232">
   <si>
     <t>Payday Super review: s 18C deadlines and the SG charge estimate</t>
   </si>
@@ -241,6 +241,12 @@
     <t>Duplicate</t>
   </si>
   <si>
+    <t>Case_variant</t>
+  </si>
+  <si>
+    <t>Sample_row</t>
+  </si>
+  <si>
     <t>EMP001</t>
   </si>
   <si>
@@ -568,15 +574,12 @@
     <t>LCR 2026/1 transition allocation reconciled and confirmed (Y/N)</t>
   </si>
   <si>
-    <t>Y</t>
+    <t>N</t>
   </si>
   <si>
     <t>Remittance-only review accepted (Y/N)</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>Holiday coverage verified until</t>
   </si>
   <si>
@@ -647,6 +650,15 @@
   </si>
   <si>
     <t>Lines assessed at a nil SG amount (nothing to assess)</t>
+  </si>
+  <si>
+    <t>As-at, assessment and coverage dates on Summary are dates</t>
+  </si>
+  <si>
+    <t>No fabricated example line from the shipped sample remains in the register</t>
+  </si>
+  <si>
+    <t>No employee ids differ only by capitalisation (treated as different people, not aligned)</t>
   </si>
   <si>
     <t>Assumptions the engine prints with every run</t>
@@ -911,8 +923,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLines" displayName="tblLines" ref="A1:BF11">
-  <tableColumns count="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblLines" displayName="tblLines" ref="A1:BH11">
+  <tableColumns count="60">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="employee_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="payment_date"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="sg_amount"/>
@@ -934,7 +946,7 @@
       <calculatedColumnFormula>IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[first_contribution_to_fund]]&amp;""))={"","0","f","false","n","no"}),0,""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Row_problem">
-      <calculatedColumnFormula>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</calculatedColumnFormula>
+      <calculatedColumnFormula>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Guard">
       <calculatedColumnFormula>IF(OR(_xlfn.ISFORMULA(tblLines[[#This Row],[employee_id]]),_xlfn.ISFORMULA(tblLines[[#This Row],[payment_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[sg_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[remitted_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[matched_amount]]),_xlfn.ISFORMULA(tblLines[[#This Row],[fund_received_date]]),_xlfn.ISFORMULA(tblLines[[#This Row],[first_contribution_to_fund]]),_xlfn.ISFORMULA(tblLines[[#This Row],[out_of_cycle]]),_xlfn.ISFORMULA(tblLines[[#This Row],[next_standard_payday]]),_xlfn.ISFORMULA(tblLines[[#This Row],[defined_benefit]])),1,0)</calculatedColumnFormula>
@@ -949,7 +961,7 @@
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Own_due">
-      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Own_pathway">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</calculatedColumnFormula>
@@ -970,19 +982,19 @@
       <calculatedColumnFormula>IF(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",MIN(ROUND(tblLines[[#This Row],[remitted_amount]],2),ROUND(tblLines[[#This Row],[sg_amount]],2)),0),IF(tblLines[[#This Row],[Remit]]&lt;&gt;"",ROUND(tblLines[[#This Row],[sg_amount]],2),0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Evidence_own">
-      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Confirmed_latest">
-      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Possible_latest">
-      <calculatedColumnFormula>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Final_due">
-      <calculatedColumnFormula>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Pathway">
-      <calculatedColumnFormula>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Possible_item4">
       <calculatedColumnFormula>IF(tblLines[[#This Row],[Final_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Possible_latest]]),tblLines[[#This Row],[Possible_latest]]&gt;tblLines[[#This Row],[Final_due]]),tblLines[[#This Row],[Possible_latest]],""))</calculatedColumnFormula>
@@ -1064,6 +1076,12 @@
     </tableColumn>
     <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Duplicate">
       <calculatedColumnFormula>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Case_variant">
+      <calculatedColumnFormula array="1">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Sample_row">
+      <calculatedColumnFormula>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1442,8 +1460,8 @@
     </row>
     <row r="11" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="str">
-        <f>'Review Checks'!B13</f>
-        <v>REVIEW</v>
+        <f>'Review Checks'!B16</f>
+        <v>BLOCKED</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -1469,7 +1487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BF11"/>
+  <dimension ref="A1:BH11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="13" customWidth="1"/>
@@ -1478,10 +1496,10 @@
     <col min="36" max="36" width="22" customWidth="1"/>
     <col min="37" max="42" width="13" customWidth="1"/>
     <col min="43" max="43" width="34" customWidth="1"/>
-    <col min="44" max="58" width="13" customWidth="1"/>
+    <col min="44" max="60" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -1656,10 +1674,16 @@
       <c r="BF1" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="BH1" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2" s="7">
         <v>46212</v>
@@ -1676,14 +1700,14 @@
         <v>46219</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L2" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -1698,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P2" s="9">
@@ -1718,7 +1742,7 @@
         <v/>
       </c>
       <c r="T2" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
       <c r="U2" s="9" t="str">
@@ -1746,23 +1770,23 @@
         <v>612</v>
       </c>
       <c r="AA2" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
       <c r="AB2" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AC2" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC2">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AD2" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
       <c r="AE2" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
       <c r="AF2" s="11" t="str">
@@ -1873,10 +1897,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG2" s="9">
+        <f t="array" ref="BG2">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH2" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B3" s="7">
         <v>46212</v>
@@ -1893,14 +1925,14 @@
         <v>46238</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L3" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -1915,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P3" s="9">
@@ -1935,7 +1967,7 @@
         <v/>
       </c>
       <c r="T3" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
       <c r="U3" s="9" t="str">
@@ -1963,23 +1995,23 @@
         <v>540</v>
       </c>
       <c r="AA3" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
       <c r="AB3" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AC3" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC3">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AD3" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
       <c r="AE3" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
       <c r="AF3" s="11" t="str">
@@ -2090,10 +2122,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG3" s="9">
+        <f t="array" ref="BG3">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH3" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="7">
         <v>46212</v>
@@ -2108,14 +2148,14 @@
       <c r="F4" s="8"/>
       <c r="G4" s="7"/>
       <c r="H4" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L4" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -2130,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P4" s="9">
@@ -2150,7 +2190,7 @@
         <v/>
       </c>
       <c r="T4" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
       <c r="U4" s="9" t="str">
@@ -2178,23 +2218,23 @@
         <v>318</v>
       </c>
       <c r="AA4" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>possible</v>
       </c>
       <c r="AB4" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AC4" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC4">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AD4" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
       <c r="AE4" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
       <c r="AF4" s="11" t="str">
@@ -2305,10 +2345,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG4" s="9">
+        <f t="array" ref="BG4">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH4" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B5" s="7">
         <v>46212</v>
@@ -2321,14 +2369,14 @@
       <c r="F5" s="8"/>
       <c r="G5" s="7"/>
       <c r="H5" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L5" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -2343,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P5" s="9">
@@ -2363,7 +2411,7 @@
         <v/>
       </c>
       <c r="T5" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46223</v>
       </c>
       <c r="U5" s="9" t="str">
@@ -2391,23 +2439,23 @@
         <v>0</v>
       </c>
       <c r="AA5" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>possible</v>
       </c>
       <c r="AB5" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AC5" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC5">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AD5" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46223</v>
       </c>
       <c r="AE5" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
       <c r="AF5" s="11" t="str">
@@ -2518,10 +2566,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG5" s="9">
+        <f t="array" ref="BG5">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH5" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B6" s="7">
         <v>46212</v>
@@ -2538,14 +2594,14 @@
         <v>46239</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L6" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -2560,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P6" s="9">
@@ -2580,7 +2636,7 @@
         <v>46241</v>
       </c>
       <c r="T6" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46241</v>
       </c>
       <c r="U6" s="9" t="str">
@@ -2608,23 +2664,23 @@
         <v>450</v>
       </c>
       <c r="AA6" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
       <c r="AB6" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AC6" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC6">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AD6" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46241</v>
       </c>
       <c r="AE6" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>EXTENDED_20BD</v>
       </c>
       <c r="AF6" s="11" t="str">
@@ -2735,10 +2791,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG6" s="9">
+        <f t="array" ref="BG6">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH6" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B7" s="7">
         <v>46218</v>
@@ -2755,16 +2819,16 @@
         <v>46234</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J7" s="7">
         <v>46226</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L7" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -2779,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P7" s="9">
@@ -2799,7 +2863,7 @@
         <v/>
       </c>
       <c r="T7" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
       <c r="U7" s="9" t="str">
@@ -2827,23 +2891,23 @@
         <v>120</v>
       </c>
       <c r="AA7" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
       <c r="AB7" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AC7" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC7">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AD7" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
       <c r="AE7" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>OUT_OF_CYCLE</v>
       </c>
       <c r="AF7" s="11" t="str">
@@ -2954,10 +3018,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG7" s="9">
+        <f t="array" ref="BG7">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH7" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="7">
         <v>46212</v>
@@ -2974,14 +3046,14 @@
         <v>46216</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L8" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -2996,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P8" s="9">
@@ -3015,9 +3087,9 @@
         <f>IF(tblLines[[#This Row],[Flag_ftf]]=1,WORKDAY.INTL(tblLines[[#This Row],[payment_date]],20,1,tblHolidays[date]),"")</f>
         <v/>
       </c>
-      <c r="T8" s="11" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
-        <v/>
+      <c r="T8" s="11">
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <v>0</v>
       </c>
       <c r="U8" s="9" t="str">
         <f>IF(tblLines[[#This Row],[Flag_db]]=1,"SKIP_DB",IF(tblLines[[#This Row],[Flag_ooc]]=1,IF(AND(tblLines[[#This Row],[Flag_ftf]]=1,tblLines[[#This Row],[Due_ftf]]&gt;tblLines[[#This Row],[Due_ooc]]),"EXTENDED_20BD","OUT_OF_CYCLE"),IF(tblLines[[#This Row],[Flag_ftf]]=1,"EXTENDED_20BD","USUAL_7BD")))</f>
@@ -3044,23 +3116,23 @@
         <v>900</v>
       </c>
       <c r="AA8" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
       <c r="AB8" s="11" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v/>
       </c>
       <c r="AC8" s="11" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC8">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v/>
       </c>
       <c r="AD8" s="11" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v/>
       </c>
       <c r="AE8" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>SKIP_DB</v>
       </c>
       <c r="AF8" s="11" t="str">
@@ -3171,10 +3243,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG8" s="9">
+        <f t="array" ref="BG8">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH8" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B9" s="7">
         <v>46226</v>
@@ -3191,14 +3271,14 @@
         <v>46240</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L9" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -3213,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P9" s="9">
@@ -3233,7 +3313,7 @@
         <v/>
       </c>
       <c r="T9" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
       <c r="U9" s="9" t="str">
@@ -3261,23 +3341,23 @@
         <v>612</v>
       </c>
       <c r="AA9" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
       <c r="AB9" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>46223</v>
       </c>
       <c r="AC9" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC9">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>46223</v>
       </c>
       <c r="AD9" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
       <c r="AE9" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
       <c r="AF9" s="11" t="str">
@@ -3388,10 +3468,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG9" s="9">
+        <f t="array" ref="BG9">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH9" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B10" s="7">
         <v>46226</v>
@@ -3408,14 +3496,14 @@
         <v>46233</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L10" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -3430,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P10" s="9">
@@ -3450,7 +3538,7 @@
         <v/>
       </c>
       <c r="T10" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
       <c r="U10" s="9" t="str">
@@ -3478,23 +3566,23 @@
         <v>540</v>
       </c>
       <c r="AA10" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>confirmed</v>
       </c>
       <c r="AB10" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AC10" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC10">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>0</v>
       </c>
       <c r="AD10" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46238</v>
       </c>
       <c r="AE10" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>USUAL_7BD</v>
       </c>
       <c r="AF10" s="11" t="str">
@@ -3605,10 +3693,18 @@
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
+      <c r="BG10" s="9">
+        <f t="array" ref="BG10">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH10" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="7">
         <v>46226</v>
@@ -3625,14 +3721,14 @@
         <v>46240</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L11" s="9">
         <f>IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"1","t","true","y","yes"}),1,IF(OR(LOWER(TRIM(tblLines[[#This Row],[defined_benefit]]&amp;""))={"","0","f","false","n","no"}),0,""))</f>
@@ -3647,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="9" t="str">
-        <f>TRIM(IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
+        <f>TRIM(IF(TRIM(tblLines[[#This Row],[employee_id]]&amp;"")="","employee_id ","")&amp;IF(OR(AND(tblLines[[#This Row],[payment_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),AND(tblLines[[#This Row],[remitted_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),AND(tblLines[[#This Row],[fund_received_date]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[fund_received_date]]))),AND(tblLines[[#This Row],[next_standard_payday]]&lt;&gt;"",NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]])))),"date ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[payment_date]])),"payment_date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[payment_date]]&lt;DATE(2026,7,1)),"pre-1-Jul-2026 ","")&amp;IF(OR(AND(tblLines[[#This Row],[sg_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),tblLines[[#This Row],[sg_amount]]&lt;0)),AND(tblLines[[#This Row],[remitted_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]])),tblLines[[#This Row],[remitted_amount]]&lt;0)),AND(tblLines[[#This Row],[matched_amount]]&lt;&gt;"",OR(NOT(ISNUMBER(tblLines[[#This Row],[matched_amount]])),tblLines[[#This Row],[matched_amount]]&lt;0))),"amount ","")&amp;IF(NOT(ISNUMBER(tblLines[[#This Row],[sg_amount]])),"sg_amount ","")&amp;IF(OR(tblLines[[#This Row],[Flag_ftf]]="",tblLines[[#This Row],[Flag_ooc]]="",tblLines[[#This Row],[Flag_db]]=""),"yes/no ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"remitted_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_amount]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_date]]))),"remitted_amount-needs-date ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&gt;tblLines[[#This Row],[sg_amount]]),"matched_amount&gt;sg ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[remitted_amount]]),tblLines[[#This Row],[remitted_amount]]&gt;tblLines[[#This Row],[matched_amount]]),"remitted_amount&gt;matched ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[matched_amount]]),ISNUMBER(tblLines[[#This Row],[sg_amount]]),tblLines[[#This Row],[matched_amount]]&lt;tblLines[[#This Row],[sg_amount]],ISNUMBER(tblLines[[#This Row],[remitted_date]]),NOT(ISNUMBER(tblLines[[#This Row],[remitted_amount]]))),"partial-match-needs-remitted_amount ","")&amp;IF(AND(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[remitted_date]]),"receipt-before-remittance ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,NOT(ISNUMBER(tblLines[[#This Row],[next_standard_payday]]))),"out_of_cycle-needs-next_standard_payday ","")&amp;IF(AND(tblLines[[#This Row],[Flag_ooc]]=1,ISNUMBER(tblLines[[#This Row],[next_standard_payday]]),ISNUMBER(tblLines[[#This Row],[payment_date]]),tblLines[[#This Row],[next_standard_payday]]&lt;=tblLines[[#This Row],[payment_date]]),"next_standard_payday-not-after-payday ",""))</f>
         <v/>
       </c>
       <c r="P11" s="9">
@@ -3667,7 +3763,7 @@
         <v/>
       </c>
       <c r="T11" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),"",IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
+        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,NOT(ISNUMBER(tblLines[[#This Row],[payment_date]]))),0,IF(OR(tblLines[[#This Row],[Flag_ooc]]=1,tblLines[[#This Row],[Flag_ftf]]=1),MAX(tblLines[[#This Row],[Due_ooc]],tblLines[[#This Row],[Due_ftf]]),WORKDAY.INTL(tblLines[[#This Row],[payment_date]],7,1,tblHolidays[date])))</f>
         <v>46238</v>
       </c>
       <c r="U11" s="9" t="str">
@@ -3695,23 +3791,23 @@
         <v>450</v>
       </c>
       <c r="AA11" s="9" t="str">
-        <f>IF(OR(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
+        <f>IF(OR(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[sg_amount]]&lt;=0,tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Cap]]&lt;=0),"impossible",IF(ISNUMBER(tblLines[[#This Row],[fund_received_date]]),IF(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[Earliest_prepay]],"impossible",IF(tblLines[[#This Row],[fund_received_date]]&lt;=Summary!$B$2,IF(OR(tblLines[[#This Row],[fund_received_date]]&lt;tblLines[[#This Row],[payment_date]],tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]]),"confirmed",IF(tblLines[[#This Row],[fund_received_date]]&gt;tblLines[[#This Row],[Own_due]],"impossible","possible")),IF(tblLines[[#This Row],[fund_received_date]]&lt;=tblLines[[#This Row],[Own_due]],"possible","impossible"))),IF(AND(ISNUMBER(tblLines[[#This Row],[remitted_date]]),tblLines[[#This Row],[remitted_date]]&gt;tblLines[[#This Row],[Own_due]]),"impossible","possible")))</f>
         <v>impossible</v>
       </c>
       <c r="AB11" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"confirmed"))</f>
+        <f t="array" ref="AB11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]="confirmed")*tblLines[Own_due])))</f>
         <v>46241</v>
       </c>
       <c r="AC11" s="11">
-        <f>IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=""),"",_xlfn.MAXIFS(tblLines[Own_due],tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],"&lt;"&amp;tblLines[[#This Row],[payment_date]],tblLines[Evidence_own],"&lt;&gt;impossible"))</f>
+        <f t="array" ref="AC11">IF(OR(tblLines[[#This Row],[Flag_db]]=1,tblLines[[#This Row],[Own_due]]=0),"",SUMPRODUCT(MAX(EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])*(tblLines[payment_date]&lt;tblLines[[#This Row],[payment_date]])*(tblLines[Evidence_own]&lt;&gt;"impossible")*tblLines[Own_due])))</f>
         <v>46241</v>
       </c>
       <c r="AD11" s="11">
-        <f>IF(tblLines[[#This Row],[Own_due]]="","",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,"",IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),tblLines[[#This Row],[Confirmed_latest]],tblLines[[#This Row],[Own_due]]))</f>
         <v>46241</v>
       </c>
       <c r="AE11" s="9" t="str">
-        <f>IF(tblLines[[#This Row],[Own_due]]="",tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
+        <f>IF(tblLines[[#This Row],[Own_due]]=0,tblLines[[#This Row],[Own_pathway]],IF(AND(ISNUMBER(tblLines[[#This Row],[Confirmed_latest]]),tblLines[[#This Row],[Confirmed_latest]]&gt;tblLines[[#This Row],[Own_due]]),"ITEM4_ALIGNED",tblLines[[#This Row],[Own_pathway]]))</f>
         <v>ITEM4_ALIGNED</v>
       </c>
       <c r="AF11" s="11" t="str">
@@ -3821,6 +3917,14 @@
       <c r="BF11" s="9">
         <f>IF(COUNTIFS(tblLines[employee_id],tblLines[[#This Row],[employee_id]],tblLines[payment_date],tblLines[[#This Row],[payment_date]],tblLines[sg_amount],tblLines[[#This Row],[sg_amount]],tblLines[remitted_date],tblLines[[#This Row],[remitted_date]]&amp;"",tblLines[fund_received_date],tblLines[[#This Row],[fund_received_date]]&amp;"")&gt;1,1,0)</f>
         <v>0</v>
+      </c>
+      <c r="BG11" s="9">
+        <f t="array" ref="BG11">IF(COUNTIF(tblLines[employee_id],tblLines[[#This Row],[employee_id]])&gt;SUMPRODUCT(--EXACT(tblLines[employee_id],tblLines[[#This Row],[employee_id]])),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH11" s="9">
+        <f>IF(AND(ISNUMBER(MATCH(tblLines[[#This Row],[employee_id]],{"EMP001","EMP002","EMP003","EMP004","EMP005","EMP006","EMP007","EMP001","EMP002","EMP005"},0)),ISNUMBER(MATCH(tblLines[[#This Row],[payment_date]],{46212,46212,46212,46212,46212,46218,46212,46226,46226,46226},0))),1,0)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3846,30 +3950,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3883,10 +3987,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3900,10 +4004,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -3917,10 +4021,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3934,13 +4038,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3954,10 +4058,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3971,10 +4075,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -3988,13 +4092,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4008,10 +4112,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4025,13 +4129,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4045,13 +4149,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4065,13 +4169,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4085,13 +4189,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4105,13 +4209,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4125,10 +4229,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4142,13 +4246,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -4162,10 +4266,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -4179,10 +4283,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -4196,10 +4300,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4213,13 +4317,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4233,13 +4337,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4253,10 +4357,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -4270,10 +4374,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4287,13 +4391,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4307,10 +4411,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4324,10 +4428,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4359,13 +4463,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4373,10 +4477,10 @@
         <v>46023</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4384,10 +4488,10 @@
         <v>46048</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4395,10 +4499,10 @@
         <v>46083</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4406,10 +4510,10 @@
         <v>46090</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4417,10 +4521,10 @@
         <v>46115</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4428,10 +4532,10 @@
         <v>46116</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4439,10 +4543,10 @@
         <v>46117</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4450,10 +4554,10 @@
         <v>46118</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4461,10 +4565,10 @@
         <v>46137</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4472,10 +4576,10 @@
         <v>46139</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4483,10 +4587,10 @@
         <v>46146</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4494,10 +4598,10 @@
         <v>46174</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4505,10 +4609,10 @@
         <v>46181</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4516,10 +4620,10 @@
         <v>46237</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4527,10 +4631,10 @@
         <v>46290</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -4538,10 +4642,10 @@
         <v>46300</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -4549,10 +4653,10 @@
         <v>46381</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -4560,10 +4664,10 @@
         <v>46382</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -4571,10 +4675,10 @@
         <v>46384</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4582,10 +4686,10 @@
         <v>46388</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -4593,10 +4697,10 @@
         <v>46413</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -4604,10 +4708,10 @@
         <v>46447</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -4615,10 +4719,10 @@
         <v>46454</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -4626,10 +4730,10 @@
         <v>46472</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -4637,10 +4741,10 @@
         <v>46473</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -4648,10 +4752,10 @@
         <v>46474</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -4659,10 +4763,10 @@
         <v>46475</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -4670,10 +4774,10 @@
         <v>46502</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,10 +4785,10 @@
         <v>46503</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -4692,10 +4796,10 @@
         <v>46510</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -4703,10 +4807,10 @@
         <v>46538</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -4714,10 +4818,10 @@
         <v>46545</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -4725,10 +4829,10 @@
         <v>46552</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -4736,10 +4840,10 @@
         <v>46601</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,10 +4851,10 @@
         <v>46664</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,10 +4862,10 @@
         <v>46746</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,10 +4873,10 @@
         <v>46747</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,10 +4884,10 @@
         <v>46748</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -4791,20 +4895,20 @@
         <v>46749</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -4825,22 +4929,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -4857,10 +4961,10 @@
         <v>365</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4877,10 +4981,10 @@
         <v>365</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -4897,7 +5001,7 @@
         <v>365</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -4915,7 +5019,7 @@
         <v>365</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -4933,7 +5037,7 @@
         <v>366</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -4951,7 +5055,7 @@
         <v>365</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -4969,13 +5073,13 @@
         <v>365</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F8" s="12"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -4997,13 +5101,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B2" s="13">
         <v>46244</v>
@@ -5011,21 +5115,21 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B3" s="13"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>178</v>
@@ -5033,7 +5137,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B6" s="13">
         <v>46630</v>
@@ -5041,7 +5145,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B7" s="11">
         <f>_xlfn.MAXIFS(tblGic[to],tblGic[basis],"known")</f>
@@ -5050,13 +5154,13 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B9" s="5"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B10" s="9">
         <f>COUNTIF(tblLines[Verdict],"ON_TIME")</f>
@@ -5065,7 +5169,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B11" s="9">
         <f>COUNTIF(tblLines[Verdict],"AT_RISK")</f>
@@ -5074,7 +5178,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B12" s="9">
         <f>COUNTIF(tblLines[Verdict],"LATE")</f>
@@ -5083,7 +5187,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B13" s="9">
         <f>COUNTIF(tblLines[Verdict],"UNPAID")</f>
@@ -5092,7 +5196,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B14" s="9">
         <f>COUNTIF(tblLines[Verdict],"UNKNOWN")</f>
@@ -5101,7 +5205,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B15" s="9">
         <f>COUNTIF(tblLines[Verdict],"SKIPPED")</f>
@@ -5110,7 +5214,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" s="9">
         <f>SUM(tblLines[Exposed])</f>
@@ -5119,7 +5223,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" s="10">
         <f>ROUND(SUM(tblLines[Shortfall_r]),2)</f>
@@ -5128,7 +5232,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B18" s="10">
         <f>ROUND(SUM(tblLines[NEC_r]),2)</f>
@@ -5137,7 +5241,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B19" s="10">
         <f>ROUND(SUM(tblLines[SGC_low]),2)</f>
@@ -5146,7 +5250,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B20" s="10">
         <f>ROUND(SUM(tblLines[SGC_high]),2)</f>
@@ -5155,7 +5259,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" s="9">
         <f>SUMPRODUCT(--(tblLines[Unassessable_between]&lt;&gt;""))</f>
@@ -5164,7 +5268,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B22" s="9" t="str">
         <f>IF(AND(SUM(tblLines[Assessable])&gt;0,SUMPRODUCT(tblLines[Assessable]*tblLines[Receipt_established])=0),"YES","NO")</f>
@@ -5176,8 +5280,8 @@
         <v>7</v>
       </c>
       <c r="B24" s="15" t="str">
-        <f>'Review Checks'!B13</f>
-        <v>REVIEW</v>
+        <f>'Review Checks'!B16</f>
+        <v>BLOCKED</v>
       </c>
     </row>
   </sheetData>
@@ -5193,9 +5297,15 @@
       <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation type="list" sqref="B4:B5" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="greaterThan" sqref="B2 B6" xr:uid="{00000000-0002-0000-0500-000002000000}">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" sqref="B3" xr:uid="{00000000-0002-0000-0500-000003000000}">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5204,7 +5314,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -5215,21 +5325,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B2" s="9" t="str">
         <f>IF(C2=0,"PASS","BLOCKED")</f>
@@ -5246,7 +5356,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B3" s="9" t="str">
         <f>IF(C3=0,"PASS","BLOCKED")</f>
@@ -5263,11 +5373,11 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B4" s="9" t="str">
         <f>IF(OR(C4=0,Summary!$B$4="Y"),"PASS","BLOCKED")</f>
-        <v>PASS</v>
+        <v>BLOCKED</v>
       </c>
       <c r="C4" s="9">
         <f>SUM(tblLines[Transition_row])</f>
@@ -5280,7 +5390,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B5" s="9" t="str">
         <f>IF(C5=0,"PASS","REVIEW")</f>
@@ -5297,7 +5407,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B6" s="9" t="str">
         <f>IF(C6=0,"PASS","REVIEW")</f>
@@ -5314,7 +5424,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" s="9" t="str">
         <f>IF(OR(Summary!B22="NO",Summary!$B$5="Y"),"PASS","REVIEW")</f>
@@ -5328,7 +5438,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B8" s="9" t="str">
         <f>IF(C8=0,"PASS","NOTE")</f>
@@ -5345,7 +5455,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B9" s="9" t="str">
         <f>IF(C9=0,"PASS","NOTE")</f>
@@ -5362,7 +5472,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B10" s="9" t="str">
         <f>IF(C10=0,"PASS","NOTE")</f>
@@ -5379,7 +5489,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B11" s="9" t="str">
         <f>IF(C11=0,"PASS","NOTE")</f>
@@ -5394,53 +5504,101 @@
         <v/>
       </c>
     </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="9" t="str">
+        <f>IF(AND(ISNUMBER(Summary!$B$2),OR(Summary!$B$3="",ISNUMBER(Summary!$B$3)),ISNUMBER(Summary!$B$6)),"PASS","BLOCKED")</f>
+        <v>PASS</v>
+      </c>
+      <c r="C12" s="9">
+        <f>Summary!$B$2</f>
+        <v>46244</v>
+      </c>
+      <c r="D12" s="9"/>
+    </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="9" t="str">
+        <f>IF(C13=0,"PASS","REVIEW")</f>
+        <v>REVIEW</v>
+      </c>
+      <c r="C13" s="9">
+        <f>SUM(tblLines[Sample_row])</f>
+        <v>10</v>
+      </c>
+      <c r="D13" s="9" t="str">
+        <f t="array" ref="D13">IF(C13=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Sample_row]=1)*(ROW(tblLines[employee_id])-1)))))</f>
+        <v>EMP005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="9" t="str">
+        <f>IF(C14=0,"PASS","NOTE")</f>
+        <v>PASS</v>
+      </c>
+      <c r="C14" s="9">
+        <f>SUM(tblLines[Case_variant])</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="str">
+        <f t="array" ref="D14">IF(C14=0,"",INDEX(tblLines[employee_id],SUMPRODUCT(MAX((tblLines[Case_variant]=1)*(ROW(tblLines[employee_id])-1)))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="15" t="str">
-        <f>IF(COUNTIF(B2:B11,"BLOCKED")&gt;0,"BLOCKED",IF(COUNTIF(B2:B11,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
-        <v>REVIEW</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>206</v>
+      <c r="B16" s="15" t="str">
+        <f>IF(COUNTIF(B2:B14,"BLOCKED")&gt;0,"BLOCKED",IF(COUNTIF(B2:B14,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
+        <v>BLOCKED</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1"/>
-  <conditionalFormatting sqref="B2:B13">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"BLOCKED"</formula>
     </cfRule>
@@ -5466,74 +5624,74 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
